--- a/output_data/charts/M100000US3918000.xlsx
+++ b/output_data/charts/M100000US3918000.xlsx
@@ -170,10 +170,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -248,16 +248,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -331,6 +334,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -361,10 +367,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -439,16 +445,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$26</c:f>
+              <c:f>Sheet1!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -522,6 +531,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -552,10 +564,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -630,16 +642,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$26</c:f>
+              <c:f>Sheet1!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -674,46 +689,49 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>33</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>23</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>74</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>54</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>56</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>27</c:v>
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -743,10 +761,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -821,16 +839,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$26</c:f>
+              <c:f>Sheet1!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -880,19 +901,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -904,7 +925,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -934,10 +958,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1012,16 +1036,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$26</c:f>
+              <c:f>Sheet1!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1095,6 +1122,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1125,10 +1155,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1203,16 +1233,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$26</c:f>
+              <c:f>Sheet1!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1286,6 +1319,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1316,10 +1352,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1394,16 +1430,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$26</c:f>
+              <c:f>Sheet1!$H$2:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -1447,36 +1486,39 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1886,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
@@ -2222,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
@@ -2248,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -2300,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
         <v>2</v>
@@ -2312,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2326,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -2338,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2352,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -2381,7 +2423,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -2390,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2404,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -2416,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2430,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -2456,10 +2498,10 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
@@ -2482,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -2508,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
@@ -2534,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
@@ -2546,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2560,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -2572,6 +2614,32 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>66</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
         <v>0</v>
       </c>
     </row>
